--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/1733-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/1733-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E083994-5E23-4416-B089-CF3F9BC4F9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{883BA44F-627A-4787-B83D-0410F126A8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{3AED5997-1FD5-4CA7-A2FF-E3FA66A31DCE}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{8BD4E29E-D505-4D2E-9F5E-4CE27F77F91A}"/>
   </bookViews>
   <sheets>
     <sheet name="1733-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1261,23 +1261,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D882ACD-183A-418C-9BCB-67A1C92336F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6352B4FD-4B60-4A3E-A4DB-29AFE1368232}">
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="13" width="11.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.77734375" customWidth="1"/>
+    <col min="1" max="3" width="8.54296875" customWidth="1"/>
+    <col min="4" max="6" width="9.08984375" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" customWidth="1"/>
+    <col min="10" max="10" width="7.6328125" customWidth="1"/>
+    <col min="11" max="13" width="8.54296875" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="9.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1308,7 +1308,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="16"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1359,7 +1359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="17"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1396,7 +1396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2025</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2024</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2023</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2022</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2021</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2020</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2018</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2017</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2016</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2015</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2014</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2013</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2012</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2011</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2010</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2009</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="10">
         <v>2008</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2007</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="10">
         <v>2006</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2005</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="10">
         <v>2004</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2003</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="10">
         <v>2002</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>2001</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="10">
         <v>2000</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1999</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="10">
         <v>1998</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A32" s="6">
         <v>1997</v>
       </c>
